--- a/aggregate_results.xlsx
+++ b/aggregate_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R197"/>
+  <dimension ref="A1:R218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13344,6 +13344,1380 @@
         <v>13.01887607037101</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ERC GARCH</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0.07859346067340001</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.1753749832390856</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.1526357982691285</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1.148976748756299</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.5194554554638544</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0.7225078167558244</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-0.5403729861150941</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0.1454429860353167</v>
+      </c>
+      <c r="P198" t="n">
+        <v>-0.0268914250716076</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>-0.3867834823732844</v>
+      </c>
+      <c r="R198" t="n">
+        <v>14.91473182976697</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ERC Historical</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0816020385517317</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.1789224289159041</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.1743257421603739</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1.026368376228115</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.5282325716033905</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0.7370007892610324</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-0.5483318500979608</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.1488187099420786</v>
+      </c>
+      <c r="P199" t="n">
+        <v>-0.0273973650975311</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>-0.3511291222452423</v>
+      </c>
+      <c r="R199" t="n">
+        <v>14.10503159668562</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>HRP GARCH</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>0.077772884465971</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.1638111523466912</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.1410508616358103</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1.16136229475611</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.539476083916224</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0.7479822652010252</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-0.5004702253583356</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0.155399623244891</v>
+      </c>
+      <c r="P200" t="n">
+        <v>-0.0251137180470326</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>-0.4394551712534288</v>
+      </c>
+      <c r="R200" t="n">
+        <v>16.50806294863809</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>HRP Historical</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0820562513047737</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.1694507260497262</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.1644332282945237</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1.030513891913716</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.5504582037041982</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.7675309771717594</v>
+      </c>
+      <c r="N201" t="n">
+        <v>-0.5186698428317368</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0.158205171244926</v>
+      </c>
+      <c r="P201" t="n">
+        <v>-0.0259393203337718</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>-0.3582740893749187</v>
+      </c>
+      <c r="R201" t="n">
+        <v>15.01573027910553</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>MVP GARCH</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>0.07783759043932841</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.1405225313013997</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.1119619489725547</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.255091864610592</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0.6040491100965397</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0.8361761921720006</v>
+      </c>
+      <c r="N202" t="n">
+        <v>-0.4225806752150903</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0.1841958116038073</v>
+      </c>
+      <c r="P202" t="n">
+        <v>-0.0209629866898065</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>-0.6438548833775258</v>
+      </c>
+      <c r="R202" t="n">
+        <v>19.88733197346657</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>MVP Historical</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>0.0806479287664814</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.1404417262293761</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0.134058731365344</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1.04761342136408</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.6227025824139129</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.8731786350205899</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-0.3956562327208101</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0.203833333325472</v>
+      </c>
+      <c r="P203" t="n">
+        <v>-0.0208836380798659</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>-0.2732089061738659</v>
+      </c>
+      <c r="R203" t="n">
+        <v>18.14625494428417</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0811612308525842</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.1897470034887824</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0.1859702753708027</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1.020308235337337</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.506503033311383</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0.7072695815170713</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-0.5723881257469503</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.1417940505783048</v>
+      </c>
+      <c r="P204" t="n">
+        <v>-0.0290434418190043</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>-0.3311670920354198</v>
+      </c>
+      <c r="R204" t="n">
+        <v>13.03341859839044</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ERC GARCH</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>0.07761013940990311</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.177718950166994</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0.1546759167500556</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1.148976220093618</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.5097821704677037</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0.7098921072808854</v>
+      </c>
+      <c r="N205" t="n">
+        <v>-0.5393666987997511</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.1438912331491885</v>
+      </c>
+      <c r="P205" t="n">
+        <v>-0.0273395298331514</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>-0.3481727603103057</v>
+      </c>
+      <c r="R205" t="n">
+        <v>14.12191982639725</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ERC Historical</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>0.08048790125569449</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.1818541454187814</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0.1770358736781451</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1.027216358134262</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0.516953938223972</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0.7215856949024118</v>
+      </c>
+      <c r="N206" t="n">
+        <v>-0.549086889891506</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0.1465849990911239</v>
+      </c>
+      <c r="P206" t="n">
+        <v>-0.0279416232019672</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>-0.3303325437107022</v>
+      </c>
+      <c r="R206" t="n">
+        <v>13.57102027049326</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>HRP GARCH</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0761510966729583</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.1657747304405745</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0.1428396541030187</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1.16056519095891</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.5259342376732037</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0.7301599969250364</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-0.498616317681046</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0.152724838663765</v>
+      </c>
+      <c r="P207" t="n">
+        <v>-0.0254830786524852</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>-0.3962410995773691</v>
+      </c>
+      <c r="R207" t="n">
+        <v>15.679107107057</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>HRP Historical</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>0.0805086280688465</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.1721976697086529</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0.1670029618594886</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1.031105483347864</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.5360983374474519</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0.7476221807452923</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-0.5203347719564111</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0.1547246742056877</v>
+      </c>
+      <c r="P208" t="n">
+        <v>-0.0264260073702358</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>-0.3553603236114699</v>
+      </c>
+      <c r="R208" t="n">
+        <v>14.63192060387699</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>MVP GARCH</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>0.0714702222388203</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.1425567128534349</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.1136403469326462</v>
+      </c>
+      <c r="K209" t="n">
+        <v>1.254455100686442</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.5558428718991888</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.769569993184501</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-0.422104950382971</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0.1693186070762171</v>
+      </c>
+      <c r="P209" t="n">
+        <v>-0.0213519712494439</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>-0.5437353708251402</v>
+      </c>
+      <c r="R209" t="n">
+        <v>18.48814874600223</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>MVP Historical</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0745402694494854</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.1431763808303976</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.1362522527356836</v>
+      </c>
+      <c r="K210" t="n">
+        <v>1.050818448544452</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.5739236702617372</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0.8039095465098127</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-0.3966827499362665</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0.1879090267007112</v>
+      </c>
+      <c r="P210" t="n">
+        <v>-0.0213503747819867</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>-0.2638452332127115</v>
+      </c>
+      <c r="R210" t="n">
+        <v>17.46255642352979</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>0.0807590762192143</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.1921736399844214</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.1883814732394583</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1.020130253149378</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.500569619661717</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.6997304306850759</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-0.572388125746951</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0.1410914597744771</v>
+      </c>
+      <c r="P211" t="n">
+        <v>-0.0294982674351805</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>-0.3039229363677228</v>
+      </c>
+      <c r="R211" t="n">
+        <v>12.45101155212773</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ERC GARCH</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>0.1097725413015946</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.1707960416722447</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.1555953404022608</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1.097693807736694</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.6956766476675409</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0.9737720274600776</v>
+      </c>
+      <c r="N212" t="n">
+        <v>-0.3744544480014269</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0.2931532577259607</v>
+      </c>
+      <c r="P212" t="n">
+        <v>-0.0259793331097737</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>-0.5095464761403711</v>
+      </c>
+      <c r="R212" t="n">
+        <v>13.01304168372992</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ERC Historical</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>0.1120899051362138</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.1750376316255579</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.1833367262133068</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0.9547330490777224</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.6949321004508144</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.9754283955621518</v>
+      </c>
+      <c r="N213" t="n">
+        <v>-0.3731963699249212</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0.3003510059831606</v>
+      </c>
+      <c r="P213" t="n">
+        <v>-0.0266194876348937</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>-0.4721096956164199</v>
+      </c>
+      <c r="R213" t="n">
+        <v>12.6069512804199</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>HRP GARCH</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>0.1050606859351865</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.1602257068895982</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0.1446140676289648</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1.107953807790595</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.7040816516272729</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.9802778341417248</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-0.3686524787879708</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0.2849857032851036</v>
+      </c>
+      <c r="P214" t="n">
+        <v>-0.024399477799189</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>-0.6150274920183226</v>
+      </c>
+      <c r="R214" t="n">
+        <v>14.32260554725912</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>HRP Historical</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>0.1093531413588966</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.166691543231283</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.173255319560448</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.9621150083829034</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.7063738661852974</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.9889971183785328</v>
+      </c>
+      <c r="N215" t="n">
+        <v>-0.3654057653054008</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.2992649589628146</v>
+      </c>
+      <c r="P215" t="n">
+        <v>-0.0253735856062374</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>-0.5355388353508558</v>
+      </c>
+      <c r="R215" t="n">
+        <v>13.49593954376045</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>MVP GARCH</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>GARCH</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>0.08943263586839389</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.1392548346783222</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.1157829431645898</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1.202723223923978</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.6852074448994442</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.9448317620483376</v>
+      </c>
+      <c r="N216" t="n">
+        <v>-0.347842471999471</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0.2571067165959247</v>
+      </c>
+      <c r="P216" t="n">
+        <v>-0.0207680766817415</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>-0.8859220127431008</v>
+      </c>
+      <c r="R216" t="n">
+        <v>14.41598814746534</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>MVP Historical</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0854133554674254</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.1401085067512505</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.1410757958703506</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0.993143479268484</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.6553447535593687</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.9158973084015122</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-0.3059790134213648</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0.2791477575940884</v>
+      </c>
+      <c r="P217" t="n">
+        <v>-0.0207455502611175</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>-0.5036312196881746</v>
+      </c>
+      <c r="R217" t="n">
+        <v>14.55195397640659</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TRBC</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>0.1133561351841887</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.1836630504957224</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.1940585079975147</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0.9464313231660758</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.6769378263897007</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.9514912334118404</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-0.3826981259066593</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0.2962024831337598</v>
+      </c>
+      <c r="P218" t="n">
+        <v>-0.0279164620449943</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>-0.4311971692338169</v>
+      </c>
+      <c r="R218" t="n">
+        <v>11.82398618740183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
